--- a/yoseftal/assets/Yoseftal_BOQ_HE.xlsx
+++ b/yoseftal/assets/Yoseftal_BOQ_HE.xlsx
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="117">
   <si>
     <t xml:space="preserve">כתב כמויות ותקציב</t>
   </si>
@@ -218,6 +218,9 @@
     <t xml:space="preserve">קומפלט</t>
   </si>
   <si>
+    <t xml:space="preserve">סכום ביניים</t>
+  </si>
+  <si>
     <t xml:space="preserve">רשת וארון</t>
   </si>
   <si>
@@ -230,7 +233,7 @@
     <t xml:space="preserve">סוף המסדרון · רשת Wi-Fi ע"י אחרים</t>
   </si>
   <si>
-    <t xml:space="preserve">כבלים (+ רזרבה, ראה גיליון כבלים)</t>
+    <t xml:space="preserve">כבילה (אורכים מהמודל + רזרבה, ראה גיליון כבלים)</t>
   </si>
   <si>
     <t xml:space="preserve">BUS</t>
@@ -263,6 +266,102 @@
     <t xml:space="preserve">חשמל 3x2.5 ממ"ר LSZH – לארון בלבד (כחול)</t>
   </si>
   <si>
+    <t xml:space="preserve">התקנה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-EQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הרכבה וחיבור התקנים (לחצנים, מנורות, משיכות, כרטיסים/LCom/BoxCom, טאבלטים)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סכום כל ההתקנים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-CAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">השחלת כבלים בתעלה / תקרה, צנרת וסימון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סכום כל הכבילה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-RACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הרכבת ארונות: מתג, שרת, פאץ' פנל, UPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-PRG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תכנות, הפעלה ובדיקת כל נקודת קריאה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-ASB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תוכניות עדות (As-built) ופרוטוקול מסירה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הדרכה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-USR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הדרכת צוות סיעוד / קבלה (שימוש יומיומי)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מפגש</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לפי משמרת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-TEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הדרכה טכנית לאחזקה / IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TR-DOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מדריכי משתמש וטכני (עב / אנג / ספר)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אחריות ושירות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAR-EQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אחריות לציוד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שנה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לפי היצרן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAR-INS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אחריות להתקנה ולעבודה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אחזקה מונעת ותמיכה טכנית (אופציונלי)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אופציונלי</t>
+  </si>
+  <si>
     <t xml:space="preserve">תשתית בית חולים (מקצועות אחרים)</t>
   </si>
   <si>
@@ -288,9 +387,6 @@
   </si>
   <si>
     <t xml:space="preserve">B2 · B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סכום ביניים</t>
   </si>
   <si>
     <t xml:space="preserve">סכום ביניים כולל בלתי צפוי</t>
@@ -344,7 +440,7 @@
     <numFmt numFmtId="168" formatCode="0&quot; m&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +507,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -522,7 +626,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -587,14 +691,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -607,7 +719,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -883,7 +995,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1236,45 +1348,17 @@
       <c r="H20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+      <c r="F21" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B22" s="11" t="s">
+      <c r="G21" s="17" t="n">
+        <f aca="false">SUM(G11:G20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="15" t="n">
-        <f aca="false">E22*F22</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1284,22 +1368,21 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <f aca="false">כבלים!D8</f>
-        <v>45</v>
+        <v>19</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="F24" s="14"/>
       <c r="G24" s="15" t="n">
@@ -1307,114 +1390,72 @@
         <v>0</v>
       </c>
       <c r="H24" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <f aca="false">SUM(G24:G24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="n">
+      <c r="E28" s="18" t="n">
+        <f aca="false">כבלים!D8</f>
+        <v>45</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15" t="n">
+        <f aca="false">E28*F28</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="16" t="n">
+      <c r="C29" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="18" t="n">
         <f aca="false">כבלים!D9</f>
         <v>190</v>
-      </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15" t="n">
-        <f aca="false">E25*F25</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <f aca="false">כבלים!D10</f>
-        <v>5</v>
-      </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15" t="n">
-        <f aca="false">E26*F26</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <f aca="false">כבלים!D11</f>
-        <v>10</v>
-      </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15" t="n">
-        <f aca="false">E27*F27</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>12</v>
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="15" t="n">
@@ -1422,47 +1463,51 @@
         <v>0</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="13" t="n">
-        <v>12</v>
+        <v>55</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <f aca="false">כבלים!D10</f>
+        <v>5</v>
       </c>
       <c r="F30" s="14"/>
       <c r="G30" s="15" t="n">
         <f aca="false">E30*F30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="12"/>
+      <c r="H30" s="12" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>4</v>
+        <v>55</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <f aca="false">כבלים!D11</f>
+        <v>10</v>
       </c>
       <c r="F31" s="14"/>
       <c r="G31" s="15" t="n">
@@ -1470,86 +1515,520 @@
         <v>0</v>
       </c>
       <c r="H31" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F32" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <f aca="false">SUM(G28:G31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <f aca="false">E11+E12+E13+E14+E15+E16+E19</f>
+        <v>52</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="15" t="n">
+        <f aca="false">E35*F35</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="n">
+      <c r="D36" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <f aca="false">E28+E29+E30+E31</f>
+        <v>250</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="15" t="n">
+        <f aca="false">E36*F36</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="15" t="n">
+        <f aca="false">E37*F37</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="B38" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15" t="n">
-        <f aca="false">E32*F32</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F34" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G34" s="17" t="n">
-        <f aca="false">SUM(G10:G32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F35" s="4" t="s">
+      <c r="F38" s="14"/>
+      <c r="G38" s="15" t="n">
+        <f aca="false">E38*F38</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="15" t="n">
+        <f aca="false">E39*F39</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F40" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <f aca="false">SUM(G35:G39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="15" t="n">
+        <f aca="false">E43*F43</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="15" t="n">
+        <f aca="false">E44*F44</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="15" t="n">
+        <f aca="false">E45*F45</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F46" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <f aca="false">SUM(G43:G45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="15" t="n">
+        <f aca="false">E49*F49</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="15" t="n">
+        <f aca="false">E50*F50</f>
+        <v>0</v>
+      </c>
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="15" t="n">
+        <f aca="false">E51*F51</f>
+        <v>0</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F52" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G52" s="17" t="n">
+        <f aca="false">SUM(G49:G51)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F55" s="14"/>
+      <c r="G55" s="15" t="n">
+        <f aca="false">E55*F55</f>
+        <v>0</v>
+      </c>
+      <c r="H55" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F56" s="14"/>
+      <c r="G56" s="15" t="n">
+        <f aca="false">E56*F56</f>
+        <v>0</v>
+      </c>
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" s="14"/>
+      <c r="G57" s="15" t="n">
+        <f aca="false">E57*F57</f>
+        <v>0</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="14"/>
+      <c r="G58" s="15" t="n">
+        <f aca="false">E58*F58</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F59" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G59" s="17" t="n">
+        <f aca="false">SUM(G55:G58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F61" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G61" s="17" t="n">
+        <f aca="false">G21+G25+G32+G40+G46+G52+G59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F62" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="15" t="n">
-        <f aca="false">G34*$C$6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F36" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" s="17" t="n">
-        <f aca="false">G34+G35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F37" s="4" t="s">
+      <c r="G62" s="15" t="n">
+        <f aca="false">G61*$C$6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F63" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G63" s="17" t="n">
+        <f aca="false">G61+G62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F64" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="15" t="n">
-        <f aca="false">G36*$C$7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F38" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G38" s="20" t="n">
-        <f aca="false">G36+G37</f>
+      <c r="G64" s="15" t="n">
+        <f aca="false">G63*$C$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F65" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G65" s="22" t="n">
+        <f aca="false">G63+G64</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
     <mergeCell ref="E5:H7"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A54:H54"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1577,13 +2056,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>74</v>
+      <c r="A1" s="23" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="B3" s="7" t="n">
         <v>0.15</v>
@@ -1591,82 +2070,82 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="22" t="n">
+        <v>108</v>
+      </c>
+      <c r="B4" s="24" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>78</v>
+      <c r="C7" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="24" t="n">
+        <v>54</v>
+      </c>
+      <c r="C8" s="26" t="n">
         <v>35.8</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="27" t="n">
         <f aca="false">ROUNDUP(C8*(1+$B$3)/$B$4,0)*$B$4</f>
         <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="C9" s="26" t="n">
         <v>161</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="27" t="n">
         <f aca="false">ROUNDUP(C9*(1+$B$3)/$B$4,0)*$B$4</f>
         <v>190</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="C10" s="26" t="n">
         <v>1.8</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="27" t="n">
         <f aca="false">ROUNDUP(C10*(1+$B$3)/$B$4,0)*$B$4</f>
         <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="24" t="n">
+        <v>62</v>
+      </c>
+      <c r="C11" s="26" t="n">
         <v>5.5</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="27" t="n">
         <f aca="false">ROUNDUP(C11*(1+$B$3)/$B$4,0)*$B$4</f>
         <v>10</v>
       </c>
@@ -1694,33 +2173,33 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>79</v>
+      <c r="A1" s="23" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>80</v>
+      <c r="A3" s="28" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>81</v>
+      <c r="A4" s="28" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>82</v>
+      <c r="A5" s="28" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>83</v>
+      <c r="A6" s="28" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
-        <v>84</v>
+      <c r="A7" s="28" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
